--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-large_idd20k.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-large_idd20k.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>110.4978806972504</v>
+        <v>211.2076306343078</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559999942779541</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0436274654542405</v>
+        <v>0.0445255056644479</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7985913753509521</v>
+        <v>0.8009325861930847</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7879244089126587</v>
+        <v>0.7887858748435974</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7881274223327637</v>
+        <v>0.7883997559547424</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7873462438583374</v>
+        <v>0.7872225642204285</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0432130210101604</v>
+        <v>0.0429387725889682</v>
       </c>
       <c r="K2" t="n">
-        <v>110.1715888977051</v>
+        <v>99.792870759964</v>
       </c>
       <c r="L2" t="n">
-        <v>2.47994327545166</v>
+        <v>2.791815280914306</v>
       </c>
       <c r="M2" t="n">
-        <v>23.4287850856781</v>
+        <v>24.09911966323853</v>
       </c>
       <c r="N2" t="n">
-        <v>15.47478461265564</v>
+        <v>15.96792364120483</v>
       </c>
       <c r="O2" t="n">
-        <v>0.008888685575095499</v>
+        <v>0.0100065063832054</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0839741400920362</v>
+        <v>0.086376772986518</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0554651778231384</v>
+        <v>0.0572327012229563</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-131026</t>
+          <t>20250720-060006</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>166.7102355957031</v>
+        <v>315.7411439418793</v>
       </c>
       <c r="D3" t="n">
-        <v>1.840000033378601</v>
+        <v>2.930000066757202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0439282257698083</v>
+        <v>0.0438074938751555</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8009576797485352</v>
+        <v>0.8060427904129028</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7909181714057922</v>
+        <v>0.7941439151763916</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7902390956878662</v>
+        <v>0.7936789989471436</v>
       </c>
       <c r="I3" t="n">
-        <v>0.789509117603302</v>
+        <v>0.793429970741272</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0411603562533855</v>
+        <v>0.0426222570240497</v>
       </c>
       <c r="K3" t="n">
-        <v>90.35087442398073</v>
+        <v>91.62892079353333</v>
       </c>
       <c r="L3" t="n">
-        <v>2.383538246154785</v>
+        <v>2.459702014923096</v>
       </c>
       <c r="M3" t="n">
-        <v>23.3906831741333</v>
+        <v>23.98131370544434</v>
       </c>
       <c r="N3" t="n">
-        <v>15.24306631088257</v>
+        <v>15.63449311256409</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0085431478356802</v>
+        <v>0.008816136254204601</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0838375741008362</v>
+        <v>0.0859545294101947</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0546346462755647</v>
+        <v>0.0560376097224519</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-131542</t>
+          <t>20250720-060635</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>132.7825129032135</v>
+        <v>226.960597038269</v>
       </c>
       <c r="D4" t="n">
-        <v>1.759999990463257</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0436338230967521</v>
+        <v>0.044130506996925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7995827794075012</v>
+        <v>0.8010107278823853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7898678779602051</v>
+        <v>0.7932020425796509</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7899441719055176</v>
+        <v>0.792592465877533</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7898039817810059</v>
+        <v>0.7919518947601318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0432558171451091</v>
+        <v>0.0432083085179328</v>
       </c>
       <c r="K4" t="n">
-        <v>91.27806091308594</v>
+        <v>112.3295249938965</v>
       </c>
       <c r="L4" t="n">
-        <v>2.486225128173828</v>
+        <v>2.516344308853149</v>
       </c>
       <c r="M4" t="n">
-        <v>23.61639833450317</v>
+        <v>23.64404797554016</v>
       </c>
       <c r="N4" t="n">
-        <v>15.52030229568481</v>
+        <v>15.51453685760498</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008911201176250201</v>
+        <v>0.0090191552288643</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0846465890125561</v>
+        <v>0.0847456916686027</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0556283236404473</v>
+        <v>0.0556076589878314</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-132155</t>
+          <t>20250720-061521</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>215.2180042266846</v>
+        <v>360.0477292537689</v>
       </c>
       <c r="D5" t="n">
-        <v>2.009999990463257</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="E5" t="n">
-        <v>0.043660789579153</v>
+        <v>0.044245616399816</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8043800592422485</v>
+        <v>0.8075137138366699</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7923977971076965</v>
+        <v>0.7940849661827087</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7919085025787354</v>
+        <v>0.7929789423942566</v>
       </c>
       <c r="I5" t="n">
-        <v>0.79107266664505</v>
+        <v>0.792610228061676</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0440398789942264</v>
+        <v>0.0429855287075042</v>
       </c>
       <c r="K5" t="n">
-        <v>89.96345686912537</v>
+        <v>92.37460350990295</v>
       </c>
       <c r="L5" t="n">
-        <v>2.509843826293945</v>
+        <v>2.557039499282837</v>
       </c>
       <c r="M5" t="n">
-        <v>23.95824575424194</v>
+        <v>24.06416416168213</v>
       </c>
       <c r="N5" t="n">
-        <v>15.62871551513672</v>
+        <v>16.06493973731995</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008995856008221999</v>
+        <v>0.0091650161264617</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0858718485815123</v>
+        <v>0.0862514844504735</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0560169014879452</v>
+        <v>0.0575804291660213</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-132736</t>
+          <t>20250720-062238</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>126.4799237251282</v>
+        <v>135.3923170566559</v>
       </c>
       <c r="D6" t="n">
-        <v>1.720000028610229</v>
+        <v>1.820000052452088</v>
       </c>
       <c r="E6" t="n">
-        <v>0.044161207973957</v>
+        <v>0.0442889377474784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7959690093994141</v>
+        <v>0.7969760894775391</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7854580283164978</v>
+        <v>0.7910020351409912</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7843358516693115</v>
+        <v>0.79154372215271</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7838584184646606</v>
+        <v>0.7904616594314575</v>
       </c>
       <c r="J6" t="n">
-        <v>0.044155053794384</v>
+        <v>0.0445060729980468</v>
       </c>
       <c r="K6" t="n">
-        <v>91.36329221725464</v>
+        <v>92.7372362613678</v>
       </c>
       <c r="L6" t="n">
-        <v>2.526504516601562</v>
+        <v>2.490730285644531</v>
       </c>
       <c r="M6" t="n">
-        <v>23.81428217887878</v>
+        <v>24.31395816802979</v>
       </c>
       <c r="N6" t="n">
-        <v>15.55210280418396</v>
+        <v>15.96870017051697</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009055571744091599</v>
+        <v>0.0089273486940664</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0853558501035081</v>
+        <v>0.08714680346964079</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0557423039576486</v>
+        <v>0.0572354844821396</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-133358</t>
+          <t>20250720-063129</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>310.499226808548</v>
+        <v>1698.137496471405</v>
       </c>
       <c r="D2" t="n">
-        <v>2.75</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1503483305374781</v>
+        <v>0.1565913549240897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7557685375213623</v>
+        <v>0.8097259402275085</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7438663244247437</v>
+        <v>0.7953490018844604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7413381934165955</v>
+        <v>0.7930800914764404</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7386086583137512</v>
+        <v>0.7871069312095642</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0711686089634895</v>
+        <v>0.0737729668617248</v>
       </c>
       <c r="K2" t="n">
-        <v>265.7954707145691</v>
+        <v>275.2233033180237</v>
       </c>
       <c r="L2" t="n">
-        <v>3.692438125610352</v>
+        <v>3.861471176147461</v>
       </c>
       <c r="M2" t="n">
-        <v>13.6449282169342</v>
+        <v>13.95684814453125</v>
       </c>
       <c r="N2" t="n">
-        <v>16.38249564170837</v>
+        <v>16.93196058273315</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0132345452530836</v>
+        <v>0.0138403984808152</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0489065527488681</v>
+        <v>0.0500245453209005</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0587186223717146</v>
+        <v>0.0606880307624844</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-135757</t>
+          <t>20250718-115007</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>309.6484327316284</v>
+        <v>1326.610040903091</v>
       </c>
       <c r="D3" t="n">
-        <v>2.730000019073486</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1497441319127877</v>
+        <v>0.1563637068249144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7444974184036255</v>
+        <v>0.799574613571167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7330012321472168</v>
+        <v>0.787930428981781</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7312470078468323</v>
+        <v>0.7850078344345093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7306609153747559</v>
+        <v>0.7801093459129333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0727872401475906</v>
+        <v>0.0790983214974403</v>
       </c>
       <c r="K3" t="n">
-        <v>265.4437167644501</v>
+        <v>276.4615280628204</v>
       </c>
       <c r="L3" t="n">
-        <v>4.096804857254028</v>
+        <v>4.02959156036377</v>
       </c>
       <c r="M3" t="n">
-        <v>13.43637132644653</v>
+        <v>14.17910671234131</v>
       </c>
       <c r="N3" t="n">
-        <v>16.68696045875549</v>
+        <v>16.46771502494812</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0146838883772545</v>
+        <v>0.0144429805030959</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0481590370123531</v>
+        <v>0.050821171011976</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0598098941174032</v>
+        <v>0.0590240681897782</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-140856</t>
+          <t>20250718-122447</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>309.5793144702911</v>
+        <v>1397.175152778625</v>
       </c>
       <c r="D4" t="n">
-        <v>2.769999980926514</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1503728528817494</v>
+        <v>0.1559421627649238</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7468035817146301</v>
+        <v>0.8057184219360352</v>
       </c>
       <c r="G4" t="n">
-        <v>0.733096718788147</v>
+        <v>0.7937065362930298</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7308279275894165</v>
+        <v>0.7911221981048584</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7273112535476685</v>
+        <v>0.7848518490791321</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06585134565830229</v>
+        <v>0.0697472393512725</v>
       </c>
       <c r="K4" t="n">
-        <v>266.8067464828491</v>
+        <v>275.853835105896</v>
       </c>
       <c r="L4" t="n">
-        <v>3.87352466583252</v>
+        <v>3.642279386520386</v>
       </c>
       <c r="M4" t="n">
-        <v>13.31933784484863</v>
+        <v>13.42474007606506</v>
       </c>
       <c r="N4" t="n">
-        <v>16.54368805885315</v>
+        <v>16.71097755432129</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0138836009528047</v>
+        <v>0.0130547648262379</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0477395621679162</v>
+        <v>0.0481173479428855</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0592963729707998</v>
+        <v>0.0598959768972089</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-142014</t>
+          <t>20250718-125255</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>308.0318250656128</v>
+        <v>1400.610742092133</v>
       </c>
       <c r="D5" t="n">
-        <v>2.779999971389771</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1480476272602875</v>
+        <v>0.1566611837063516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7547438740730286</v>
+        <v>0.7995622158050537</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7337723970413208</v>
+        <v>0.7919187545776367</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7315269708633423</v>
+        <v>0.789287269115448</v>
       </c>
       <c r="I5" t="n">
-        <v>0.725859522819519</v>
+        <v>0.785477340221405</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0701826512813568</v>
+        <v>0.0767068639397621</v>
       </c>
       <c r="K5" t="n">
-        <v>265.7525317668915</v>
+        <v>276.0336818695068</v>
       </c>
       <c r="L5" t="n">
-        <v>3.695042848587036</v>
+        <v>4.243395328521729</v>
       </c>
       <c r="M5" t="n">
-        <v>13.21930074691772</v>
+        <v>14.05256819725037</v>
       </c>
       <c r="N5" t="n">
-        <v>16.28160548210144</v>
+        <v>16.58019280433655</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0132438811777313</v>
+        <v>0.015209302252766</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0473810062613538</v>
+        <v>0.0503676279471339</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0583570088964209</v>
+        <v>0.0594272143524607</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-143133</t>
+          <t>20250718-132233</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>308.7940013408661</v>
+        <v>1423.49977850914</v>
       </c>
       <c r="D6" t="n">
-        <v>2.710000038146973</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1491388132174809</v>
+        <v>0.1559107052652458</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7455408573150635</v>
+        <v>0.8041864633560181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7349135875701904</v>
+        <v>0.7903594970703125</v>
       </c>
       <c r="H6" t="n">
-        <v>0.73481684923172</v>
+        <v>0.787421703338623</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7342383861541748</v>
+        <v>0.7832230925559998</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0708416476845741</v>
+        <v>0.0714063569903373</v>
       </c>
       <c r="K6" t="n">
-        <v>263.6804895401001</v>
+        <v>276.5493903160095</v>
       </c>
       <c r="L6" t="n">
-        <v>3.741942644119263</v>
+        <v>3.823434829711914</v>
       </c>
       <c r="M6" t="n">
-        <v>13.73389291763306</v>
+        <v>14.03970909118652</v>
       </c>
       <c r="N6" t="n">
-        <v>16.37794923782349</v>
+        <v>16.68345046043396</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0134119808032948</v>
+        <v>0.0137040674900068</v>
       </c>
       <c r="P6" t="n">
-        <v>0.049225422643846</v>
+        <v>0.050321537961242</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0587023270172884</v>
+        <v>0.0597973134782579</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-144229</t>
+          <t>20250718-135155</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="C2" t="n">
-        <v>267.604017496109</v>
+        <v>1219.77889752388</v>
       </c>
       <c r="D2" t="n">
-        <v>1.480000019073486</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1292025210956732</v>
+        <v>0.133023727619857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7239250540733337</v>
+        <v>0.7802820205688477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7117064595222473</v>
+        <v>0.7685856223106384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7098253965377808</v>
+        <v>0.7668321132659912</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6916143298149109</v>
+        <v>0.7304259538650513</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0655851885676384</v>
+        <v>0.0664063468575477</v>
       </c>
       <c r="K2" t="n">
-        <v>216.472734451294</v>
+        <v>225.6952798366546</v>
       </c>
       <c r="L2" t="n">
-        <v>3.363395929336548</v>
+        <v>3.411694526672364</v>
       </c>
       <c r="M2" t="n">
-        <v>14.3955500125885</v>
+        <v>14.50111842155456</v>
       </c>
       <c r="N2" t="n">
-        <v>19.17716789245605</v>
+        <v>19.85474538803101</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0120551825424249</v>
+        <v>0.0122282957945245</v>
       </c>
       <c r="P2" t="n">
-        <v>0.051596953450138</v>
+        <v>0.0519753348442815</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06873536879016499</v>
+        <v>0.0711639619642688</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-165714</t>
+          <t>20250718-174928</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>269.8627734184265</v>
+        <v>959.104038476944</v>
       </c>
       <c r="D3" t="n">
-        <v>1.629999995231628</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1297766802211602</v>
+        <v>0.1343037265945564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7191398739814758</v>
+        <v>0.7691758871078491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7081760168075562</v>
+        <v>0.7556921243667603</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7056572437286377</v>
+        <v>0.7538420557975769</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6619431376457214</v>
+        <v>0.7082706093788147</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0653517693281173</v>
+        <v>0.0625451579689979</v>
       </c>
       <c r="K3" t="n">
-        <v>216.7226581573486</v>
+        <v>225.720867395401</v>
       </c>
       <c r="L3" t="n">
-        <v>3.343630075454712</v>
+        <v>3.26667046546936</v>
       </c>
       <c r="M3" t="n">
-        <v>14.37800669670105</v>
+        <v>15.02986836433411</v>
       </c>
       <c r="N3" t="n">
-        <v>18.80892729759216</v>
+        <v>20.07252693176269</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0119843371880097</v>
+        <v>0.0117084962920048</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0515340741817241</v>
+        <v>0.0538704959295129</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06741551002721199</v>
+        <v>0.07194454097405981</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-170643</t>
+          <t>20250718-181501</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>269.2772707939148</v>
+        <v>1431.434258460998</v>
       </c>
       <c r="D4" t="n">
-        <v>1.610000014305115</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1299538252254327</v>
+        <v>0.135016602774461</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7390404939651489</v>
+        <v>0.7716957330703735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7294886112213135</v>
+        <v>0.7654707431793213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7272133827209473</v>
+        <v>0.7638850808143616</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7008122801780701</v>
+        <v>0.6993379592895508</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0611797049641609</v>
+        <v>0.06940522789955129</v>
       </c>
       <c r="K4" t="n">
-        <v>216.6860928535461</v>
+        <v>226.4841458797455</v>
       </c>
       <c r="L4" t="n">
-        <v>3.125706195831299</v>
+        <v>3.49719500541687</v>
       </c>
       <c r="M4" t="n">
-        <v>14.30490589141846</v>
+        <v>14.98471975326538</v>
       </c>
       <c r="N4" t="n">
-        <v>19.02549862861633</v>
+        <v>19.44162273406982</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0112032480137322</v>
+        <v>0.0125347491233579</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0512720641269478</v>
+        <v>0.0537086729507719</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06819175135704771</v>
+        <v>0.06968323560598499</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-171614</t>
+          <t>20250718-183614</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>267.5146198272705</v>
+        <v>1216.168772935867</v>
       </c>
       <c r="D5" t="n">
-        <v>1.580000042915344</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1290124605099359</v>
+        <v>0.1350201421550341</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7300230264663696</v>
+        <v>0.7693449258804321</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7159059047698975</v>
+        <v>0.7588349580764771</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7126777768135071</v>
+        <v>0.7572045922279358</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6349079012870789</v>
+        <v>0.7285274267196655</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0593016482889652</v>
+        <v>0.0610094256699085</v>
       </c>
       <c r="K5" t="n">
-        <v>218.0526056289673</v>
+        <v>226.6332972049713</v>
       </c>
       <c r="L5" t="n">
-        <v>3.148338794708252</v>
+        <v>3.225802898406982</v>
       </c>
       <c r="M5" t="n">
-        <v>14.5121648311615</v>
+        <v>14.47894549369812</v>
       </c>
       <c r="N5" t="n">
-        <v>18.67809009552002</v>
+        <v>19.38223528862</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0112843684398145</v>
+        <v>0.0115620175570142</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0520149277102562</v>
+        <v>0.051895861984581</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0669465594821506</v>
+        <v>0.06947037737856621</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-172544</t>
+          <t>20250718-190519</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>309.8629789352417</v>
+        <v>1389.480852365494</v>
       </c>
       <c r="D6" t="n">
-        <v>1.409999966621399</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1286987939051219</v>
+        <v>0.1334047686595182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7263568639755249</v>
+        <v>0.7850383520126343</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7205632925033569</v>
+        <v>0.7705782651901245</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7186360359191895</v>
+        <v>0.7686198949813843</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6744477152824402</v>
+        <v>0.7107931971549988</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0596210435032844</v>
+        <v>0.0593171939253807</v>
       </c>
       <c r="K6" t="n">
-        <v>216.1123471260071</v>
+        <v>224.5037460327148</v>
       </c>
       <c r="L6" t="n">
-        <v>3.175338268280029</v>
+        <v>3.471880912780762</v>
       </c>
       <c r="M6" t="n">
-        <v>14.0300555229187</v>
+        <v>14.82607507705688</v>
       </c>
       <c r="N6" t="n">
-        <v>19.15730738639832</v>
+        <v>19.36076378822327</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0113811407465234</v>
+        <v>0.0124440176085331</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0502869373581315</v>
+        <v>0.0531400540396304</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0686641841806391</v>
+        <v>0.0693934185957823</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-173514</t>
+          <t>20250718-193049</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>853.4934160709381</v>
+        <v>3711.526425838471</v>
       </c>
       <c r="D2" t="n">
-        <v>8.819999694824219</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3326282147318125</v>
+        <v>0.3326560536476031</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7645711898803711</v>
+        <v>0.8079228401184082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7601758241653442</v>
+        <v>0.7935408353805542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7582887411117554</v>
+        <v>0.7903481721878052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2288579493761062</v>
+        <v>0.6549751758575439</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1068326607346534</v>
+        <v>0.1121824532747268</v>
       </c>
       <c r="K2" t="n">
-        <v>1772.865061283112</v>
+        <v>1853.778037548065</v>
       </c>
       <c r="L2" t="n">
-        <v>5.818650722503662</v>
+        <v>6.067195892333984</v>
       </c>
       <c r="M2" t="n">
-        <v>33.2357325553894</v>
+        <v>33.91516399383545</v>
       </c>
       <c r="N2" t="n">
-        <v>35.66782307624817</v>
+        <v>36.71845149993896</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0208553789337048</v>
+        <v>0.0217462218363225</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1191244894458401</v>
+        <v>0.1215597275764711</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1278416597714988</v>
+        <v>0.1316073530463762</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-004007</t>
+          <t>20250719-055440</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>645.5070948600769</v>
+        <v>2651.728832244873</v>
       </c>
       <c r="D3" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3282941877841949</v>
+        <v>0.3317309279854481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7229155898094177</v>
+        <v>0.8061126470565796</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7225819826126099</v>
+        <v>0.7911288738250732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.719972550868988</v>
+        <v>0.7882347106933594</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4981724619865417</v>
+        <v>0.2141021639108657</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1069636568427085</v>
+        <v>0.1155784204602241</v>
       </c>
       <c r="K3" t="n">
-        <v>1765.598149299622</v>
+        <v>1848.615552425384</v>
       </c>
       <c r="L3" t="n">
-        <v>5.827537536621094</v>
+        <v>6.232304096221924</v>
       </c>
       <c r="M3" t="n">
-        <v>33.08515024185181</v>
+        <v>33.53253412246704</v>
       </c>
       <c r="N3" t="n">
-        <v>35.8429811000824</v>
+        <v>36.26391506195069</v>
       </c>
       <c r="O3" t="n">
-        <v>0.020887231314054</v>
+        <v>0.0223380075133402</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1185847678919419</v>
+        <v>0.12018829434576</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.128469466308539</v>
+        <v>0.1299781901862031</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-012624</t>
+          <t>20250719-073001</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>649.2546217441559</v>
+        <v>2845.503630161285</v>
       </c>
       <c r="D4" t="n">
         <v>8.859999656677246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3298007821043332</v>
+        <v>0.3315923410866941</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7625968456268311</v>
+        <v>0.8071444630622864</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7501598596572876</v>
+        <v>0.8001638650894165</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7476374506950378</v>
+        <v>0.796950101852417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.57680344581604</v>
+        <v>0.5369940996170044</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1078573688864708</v>
+        <v>0.1055933088064193</v>
       </c>
       <c r="K4" t="n">
-        <v>1816.540959835052</v>
+        <v>1844.140513658524</v>
       </c>
       <c r="L4" t="n">
-        <v>5.848817110061646</v>
+        <v>5.8802809715271</v>
       </c>
       <c r="M4" t="n">
-        <v>33.51045560836792</v>
+        <v>33.99720335006714</v>
       </c>
       <c r="N4" t="n">
-        <v>35.92323803901672</v>
+        <v>37.05563569068909</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0209635021866008</v>
+        <v>0.0210762758836096</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1201091598866233</v>
+        <v>0.1218537754482693</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1287571255878735</v>
+        <v>0.1328158985329358</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-020906</t>
+          <t>20250719-084737</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>747.2683374881744</v>
+        <v>2863.753146409988</v>
       </c>
       <c r="D5" t="n">
-        <v>8.859999656677246</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3291800384010587</v>
+        <v>0.3324168510735035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.754654586315155</v>
+        <v>0.8019478917121887</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7511427998542786</v>
+        <v>0.7922053933143616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7493660449981689</v>
+        <v>0.7891817092895508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5129488110542297</v>
+        <v>0.2849306464195251</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1096685826778411</v>
+        <v>0.1118238642811775</v>
       </c>
       <c r="K5" t="n">
-        <v>1786.208805561066</v>
+        <v>1854.941435098648</v>
       </c>
       <c r="L5" t="n">
-        <v>5.605352878570557</v>
+        <v>6.167104482650757</v>
       </c>
       <c r="M5" t="n">
-        <v>33.69414830207825</v>
+        <v>34.16125345230103</v>
       </c>
       <c r="N5" t="n">
-        <v>36.28815031051636</v>
+        <v>36.95046210289001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0200908705325109</v>
+        <v>0.0221043171421174</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1207675566382733</v>
+        <v>0.1224417686462402</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1300650548764027</v>
+        <v>0.132438932268423</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-025243</t>
+          <t>20250719-100822</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>1241.387707233429</v>
+        <v>2908.240720033646</v>
       </c>
       <c r="D6" t="n">
-        <v>8.819999694824219</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3292991978426774</v>
+        <v>0.3314920475608424</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7823798656463623</v>
+        <v>0.8051818609237671</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7717862129211426</v>
+        <v>0.7987508177757263</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7675012350082397</v>
+        <v>0.7954124212265015</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6363458037376404</v>
+        <v>0.4738762080669403</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1083252653479576</v>
+        <v>0.1038564518094062</v>
       </c>
       <c r="K6" t="n">
-        <v>1775.466997385025</v>
+        <v>1854.765387535095</v>
       </c>
       <c r="L6" t="n">
-        <v>5.869872093200684</v>
+        <v>5.86062479019165</v>
       </c>
       <c r="M6" t="n">
-        <v>33.46661043167114</v>
+        <v>34.0386655330658</v>
       </c>
       <c r="N6" t="n">
-        <v>35.71104598045349</v>
+        <v>36.66395902633667</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0210389680759881</v>
+        <v>0.0210058236207586</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1199520087156671</v>
+        <v>0.1220023854231748</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1279965805751021</v>
+        <v>0.1314120395209199</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-033729</t>
+          <t>20250719-112938</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>417.9251546859741</v>
+        <v>2113.475056409836</v>
       </c>
       <c r="D2" t="n">
-        <v>7.360000133514404</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2017475192745526</v>
+        <v>0.2004082049384261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7990658283233643</v>
+        <v>0.8335310220718384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7844328880310059</v>
+        <v>0.8238037824630737</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7824428081512451</v>
+        <v>0.8214598298072815</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7769072651863098</v>
+        <v>0.8185414671897888</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08009291440248489</v>
+        <v>0.0801214575767517</v>
       </c>
       <c r="K2" t="n">
-        <v>146.9466068744659</v>
+        <v>145.0797662734985</v>
       </c>
       <c r="L2" t="n">
-        <v>4.310568571090698</v>
+        <v>4.449892282485962</v>
       </c>
       <c r="M2" t="n">
-        <v>25.35935616493225</v>
+        <v>25.18686151504517</v>
       </c>
       <c r="N2" t="n">
-        <v>20.26540160179139</v>
+        <v>20.31970405578613</v>
       </c>
       <c r="O2" t="n">
-        <v>0.015450066563049</v>
+        <v>0.0159494347042507</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0908937496950976</v>
+        <v>0.09027548930123711</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0726358480350945</v>
+        <v>0.0728304804866886</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-064052</t>
+          <t>20250719-154758</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
-        <v>418.6845555305481</v>
+        <v>2647.49517583847</v>
       </c>
       <c r="D3" t="n">
-        <v>7.400000095367432</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2019990347325801</v>
+        <v>0.2004749315330781</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7935863733291626</v>
+        <v>0.8347631692886353</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7842566967010498</v>
+        <v>0.8276669979095459</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7825710773468018</v>
+        <v>0.8248223066329956</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7721529603004456</v>
+        <v>0.8235999345779419</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0811125487089157</v>
+        <v>0.0806917995214462</v>
       </c>
       <c r="K3" t="n">
-        <v>145.7033944129944</v>
+        <v>148.261679649353</v>
       </c>
       <c r="L3" t="n">
-        <v>4.653696775436401</v>
+        <v>4.687019109725952</v>
       </c>
       <c r="M3" t="n">
-        <v>25.63416886329651</v>
+        <v>26.01577162742615</v>
       </c>
       <c r="N3" t="n">
-        <v>19.70664286613464</v>
+        <v>20.36695432662964</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0166799167578365</v>
+        <v>0.0167993516477632</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0918787414455072</v>
+        <v>0.0932464932882657</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07063312855245391</v>
+        <v>0.0729998362961635</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-065152</t>
+          <t>20250719-162734</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>416.4955866336823</v>
+        <v>1839.283390522003</v>
       </c>
       <c r="D4" t="n">
-        <v>7.480000019073486</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2016028153399626</v>
+        <v>0.2004850770820651</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7997450828552246</v>
+        <v>0.8292791843414307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7898323535919189</v>
+        <v>0.8186444044113159</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7876917123794556</v>
+        <v>0.8170033693313599</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7743711471557617</v>
+        <v>0.8111550211906433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0794506445527076</v>
+        <v>0.0802479013800621</v>
       </c>
       <c r="K4" t="n">
-        <v>141.9027893543243</v>
+        <v>166.1335399150848</v>
       </c>
       <c r="L4" t="n">
-        <v>4.227524995803833</v>
+        <v>4.352849721908569</v>
       </c>
       <c r="M4" t="n">
-        <v>25.54098010063172</v>
+        <v>25.60110807418823</v>
       </c>
       <c r="N4" t="n">
-        <v>19.99163198471069</v>
+        <v>20.13644218444824</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0151524193397986</v>
+        <v>0.0156016119064823</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0915447315434828</v>
+        <v>0.0917602439935062</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07165459492727839</v>
+        <v>0.07217362790124809</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-070251</t>
+          <t>20250719-171548</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>416.4610412120819</v>
+        <v>2474.50227856636</v>
       </c>
       <c r="D5" t="n">
-        <v>7.400000095367432</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2015350858370462</v>
+        <v>0.2006429327385766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7933654189109802</v>
+        <v>0.8359231948852539</v>
       </c>
       <c r="G5" t="n">
-        <v>0.781974732875824</v>
+        <v>0.8281614780426025</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7803269028663635</v>
+        <v>0.825705349445343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7725213766098022</v>
+        <v>0.8218453526496887</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08056151121854779</v>
+        <v>0.0799513906240463</v>
       </c>
       <c r="K5" t="n">
-        <v>167.863874912262</v>
+        <v>171.4881372451782</v>
       </c>
       <c r="L5" t="n">
-        <v>4.325030088424683</v>
+        <v>4.43171238899231</v>
       </c>
       <c r="M5" t="n">
-        <v>25.44492793083191</v>
+        <v>25.92628955841064</v>
       </c>
       <c r="N5" t="n">
-        <v>19.98957848548889</v>
+        <v>19.98648571968078</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0155018999585114</v>
+        <v>0.0158842737956713</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0912004585334477</v>
+        <v>0.0929257690265614</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0716472347150139</v>
+        <v>0.07163614953290599</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-071344</t>
+          <t>20250719-175051</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="C6" t="n">
-        <v>419.7650227546692</v>
+        <v>2731.289233922958</v>
       </c>
       <c r="D6" t="n">
-        <v>7.480000019073486</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2019279040396213</v>
+        <v>0.2003984507392434</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7992212772369385</v>
+        <v>0.8363082408905029</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7882431149482727</v>
+        <v>0.8274447917938232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7861770391464233</v>
+        <v>0.8248506784439087</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7799069881439209</v>
+        <v>0.8234127163887024</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0836219042539596</v>
+        <v>0.0799347385764122</v>
       </c>
       <c r="K6" t="n">
-        <v>146.1618223190308</v>
+        <v>144.7563796043396</v>
       </c>
       <c r="L6" t="n">
-        <v>4.351869106292725</v>
+        <v>4.3884437084198</v>
       </c>
       <c r="M6" t="n">
-        <v>25.62159466743469</v>
+        <v>25.36142635345459</v>
       </c>
       <c r="N6" t="n">
-        <v>19.83498191833496</v>
+        <v>20.16662812232971</v>
       </c>
       <c r="O6" t="n">
-        <v>0.015598097155171</v>
+        <v>0.0157291889190673</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09183367264313499</v>
+        <v>0.0909011697256436</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0710931251553224</v>
+        <v>0.0722818212269882</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-072503</t>
+          <t>20250719-183634</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>263.3640336990356</v>
+        <v>950.8857963085176</v>
       </c>
       <c r="D2" t="n">
-        <v>4.769999980926514</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1257568945487339</v>
+        <v>0.1259468567112217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7748597860336304</v>
+        <v>0.8135792016983032</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7666861414909363</v>
+        <v>0.8057218790054321</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7654731273651123</v>
+        <v>0.8028199672698975</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7626697421073914</v>
+        <v>0.7999787330627441</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0587894693017005</v>
+        <v>0.058684516698122</v>
       </c>
       <c r="K2" t="n">
-        <v>85.79419612884521</v>
+        <v>84.06671762466431</v>
       </c>
       <c r="L2" t="n">
-        <v>3.131161451339722</v>
+        <v>3.166439056396484</v>
       </c>
       <c r="M2" t="n">
-        <v>16.0870521068573</v>
+        <v>16.62206530570984</v>
       </c>
       <c r="N2" t="n">
-        <v>13.36323046684265</v>
+        <v>13.56556963920593</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0112228009008592</v>
+        <v>0.0113492439297365</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0576596849708146</v>
+        <v>0.0595772950025442</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0478968833937012</v>
+        <v>0.0486221134021718</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-091030</t>
+          <t>20250719-215229</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>264.9135122299194</v>
+        <v>1110.801471233368</v>
       </c>
       <c r="D3" t="n">
-        <v>4.659999847412109</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.125961893548568</v>
+        <v>0.1260665129456255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7761645317077637</v>
+        <v>0.8184645175933838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7630398273468018</v>
+        <v>0.8105575442314148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7601962685585022</v>
+        <v>0.8085383176803589</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7553725838661194</v>
+        <v>0.8059754371643066</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0562312863767147</v>
+        <v>0.0579109862446785</v>
       </c>
       <c r="K3" t="n">
-        <v>104.1579580307007</v>
+        <v>84.14042377471924</v>
       </c>
       <c r="L3" t="n">
-        <v>3.078730821609497</v>
+        <v>3.158691167831421</v>
       </c>
       <c r="M3" t="n">
-        <v>16.12953472137451</v>
+        <v>15.78366756439209</v>
       </c>
       <c r="N3" t="n">
-        <v>13.5074028968811</v>
+        <v>13.72171425819397</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0110348774968082</v>
+        <v>0.0113214737198258</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0578119524063602</v>
+        <v>0.0565722851770325</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0484136304547709</v>
+        <v>0.0491817715347454</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-091729</t>
+          <t>20250719-221055</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>264.5394842624664</v>
+        <v>1423.121651649475</v>
       </c>
       <c r="D4" t="n">
-        <v>4.769999980926514</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1258051116019487</v>
+        <v>0.1274474882993145</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7824647426605225</v>
+        <v>0.8219746947288513</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7712947130203247</v>
+        <v>0.8133401870727539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7693196535110474</v>
+        <v>0.8117437362670898</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7674253582954407</v>
+        <v>0.8100804090499878</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0587036050856113</v>
+        <v>0.0566738471388816</v>
       </c>
       <c r="K4" t="n">
-        <v>105.5572512149811</v>
+        <v>97.19948577880859</v>
       </c>
       <c r="L4" t="n">
-        <v>3.444916009902954</v>
+        <v>3.154383420944214</v>
       </c>
       <c r="M4" t="n">
-        <v>16.14279913902283</v>
+        <v>16.90333485603333</v>
       </c>
       <c r="N4" t="n">
-        <v>13.96761012077332</v>
+        <v>15.68528699874878</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0123473692111216</v>
+        <v>0.0113060337668251</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0578594951219456</v>
+        <v>0.0605854295915173</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0500631187124491</v>
+        <v>0.056219666662182</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-092508</t>
+          <t>20250719-223222</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>264.7108149528503</v>
+        <v>1584.681986093521</v>
       </c>
       <c r="D5" t="n">
-        <v>4.809999942779541</v>
+        <v>5.059999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1256662427137295</v>
+        <v>0.126323490464068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7781845927238464</v>
+        <v>0.8218780755996704</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7673295736312866</v>
+        <v>0.8156746625900269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7645754814147949</v>
+        <v>0.8137463331222534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.76423579454422</v>
+        <v>0.8117508888244629</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0577726140618324</v>
+        <v>0.0550873316824436</v>
       </c>
       <c r="K5" t="n">
-        <v>83.89807105064392</v>
+        <v>84.4327700138092</v>
       </c>
       <c r="L5" t="n">
-        <v>3.153408050537109</v>
+        <v>3.003417253494263</v>
       </c>
       <c r="M5" t="n">
-        <v>16.03765726089478</v>
+        <v>16.40593361854553</v>
       </c>
       <c r="N5" t="n">
-        <v>13.14134287834168</v>
+        <v>13.86163353919983</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0113025378155451</v>
+        <v>0.0107649363924525</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0574826425121676</v>
+        <v>0.0588026294571524</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0471015873775687</v>
+        <v>0.0496832743340495</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-093228</t>
+          <t>20250719-225857</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>265.1697156429291</v>
+        <v>1171.467784166336</v>
       </c>
       <c r="D6" t="n">
-        <v>4.710000038146973</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1263027514020601</v>
+        <v>0.1260347697034216</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7692790031433105</v>
+        <v>0.8134604096412659</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7567905187606812</v>
+        <v>0.8083552122116089</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7554275989532471</v>
+        <v>0.807231605052948</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7532513737678528</v>
+        <v>0.8041368126869202</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0674773827195167</v>
+        <v>0.0555816851556301</v>
       </c>
       <c r="K6" t="n">
-        <v>103.8556954860687</v>
+        <v>105.634753704071</v>
       </c>
       <c r="L6" t="n">
-        <v>3.439824342727661</v>
+        <v>3.094919919967652</v>
       </c>
       <c r="M6" t="n">
-        <v>16.05224967002869</v>
+        <v>16.10882806777954</v>
       </c>
       <c r="N6" t="n">
-        <v>13.49637365341186</v>
+        <v>13.80390334129334</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0123291195079844</v>
+        <v>0.0110929029389521</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0575349450538662</v>
+        <v>0.0577377350099625</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0483740991161715</v>
+        <v>0.0494763560619832</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-093946</t>
+          <t>20250719-232758</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>237.832412481308</v>
+        <v>1400.555305242538</v>
       </c>
       <c r="D2" t="n">
-        <v>3.589999914169312</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1139606603731711</v>
+        <v>0.1146068153412718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7452337741851807</v>
+        <v>0.806735634803772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7319251894950867</v>
+        <v>0.7994555234909058</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7302440404891968</v>
+        <v>0.7976891994476318</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7309368848800659</v>
+        <v>0.7969673871994019</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0508416034281253</v>
+        <v>0.0506798103451728</v>
       </c>
       <c r="K2" t="n">
-        <v>65.0289900302887</v>
+        <v>67.01188945770264</v>
       </c>
       <c r="L2" t="n">
-        <v>2.720578670501709</v>
+        <v>2.74858832359314</v>
       </c>
       <c r="M2" t="n">
-        <v>12.55883765220642</v>
+        <v>12.68917989730835</v>
       </c>
       <c r="N2" t="n">
-        <v>12.35314679145813</v>
+        <v>13.51380896568298</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009751178030471999</v>
+        <v>0.009851571052305099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0450137550258294</v>
+        <v>0.0454809315315711</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0442765117973409</v>
+        <v>0.0484365912748494</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-111335</t>
+          <t>20250720-021836</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="C3" t="n">
-        <v>236.8968622684479</v>
+        <v>1585.715210676193</v>
       </c>
       <c r="D3" t="n">
-        <v>3.809999942779541</v>
+        <v>3.829999923706055</v>
       </c>
       <c r="E3" t="n">
-        <v>0.113682302335898</v>
+        <v>0.1143784927594106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7364651560783386</v>
+        <v>0.8094531297683716</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7296809554100037</v>
+        <v>0.8046225309371948</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7279049158096313</v>
+        <v>0.8029451370239258</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7232409119606018</v>
+        <v>0.8021563291549683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0473505370318889</v>
+        <v>0.0503431744873523</v>
       </c>
       <c r="K3" t="n">
-        <v>65.40230894088745</v>
+        <v>68.87248253822327</v>
       </c>
       <c r="L3" t="n">
-        <v>2.571979999542236</v>
+        <v>2.699894428253174</v>
       </c>
       <c r="M3" t="n">
-        <v>12.26888585090637</v>
+        <v>12.62012505531311</v>
       </c>
       <c r="N3" t="n">
-        <v>12.61930751800537</v>
+        <v>12.84334778785706</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0092185663066029</v>
+        <v>0.0096770409614809</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0439745012577289</v>
+        <v>0.0452334231373229</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0452304928960766</v>
+        <v>0.0460335046159751</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-112003</t>
+          <t>20250720-024432</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>237.781076669693</v>
+        <v>1452.101139545441</v>
       </c>
       <c r="D4" t="n">
-        <v>3.430000066757202</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1139872533579667</v>
+        <v>0.1139648912262312</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7517397403717041</v>
+        <v>0.807955265045166</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7361663579940796</v>
+        <v>0.7989195585250854</v>
       </c>
       <c r="H4" t="n">
-        <v>0.734552800655365</v>
+        <v>0.7963964343070984</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7313451766967773</v>
+        <v>0.79375159740448</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0476618595421314</v>
+        <v>0.047112550586462</v>
       </c>
       <c r="K4" t="n">
-        <v>67.14247035980225</v>
+        <v>68.37729287147522</v>
       </c>
       <c r="L4" t="n">
-        <v>2.631992816925049</v>
+        <v>2.683174610137939</v>
       </c>
       <c r="M4" t="n">
-        <v>12.62304735183716</v>
+        <v>12.86145853996277</v>
       </c>
       <c r="N4" t="n">
-        <v>12.52435851097107</v>
+        <v>13.03606986999512</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009433666010483999</v>
+        <v>0.0096171132979854</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0452438973184127</v>
+        <v>0.0460984177059597</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0448901738744482</v>
+        <v>0.0467242647670075</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-112610</t>
+          <t>20250720-031334</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>237.1774823665619</v>
+        <v>1416.443036317825</v>
       </c>
       <c r="D5" t="n">
-        <v>3.460000038146973</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1136599344511826</v>
+        <v>0.1142938980808505</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7574619054794312</v>
+        <v>0.8091200590133667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7444512248039246</v>
+        <v>0.800571084022522</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7424291372299194</v>
+        <v>0.7985458970069885</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7366523742675781</v>
+        <v>0.7946949005126953</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0486738979816436</v>
+        <v>0.0509300678968429</v>
       </c>
       <c r="K5" t="n">
-        <v>66.93439292907715</v>
+        <v>88.97238945960999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.643672943115234</v>
+        <v>2.804058313369751</v>
       </c>
       <c r="M5" t="n">
-        <v>12.92157983779907</v>
+        <v>12.44246673583984</v>
       </c>
       <c r="N5" t="n">
-        <v>12.69753837585449</v>
+        <v>13.13793182373047</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0094755302620617</v>
+        <v>0.0100503882199632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0463139062286705</v>
+        <v>0.0445966549671679</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0455108902360376</v>
+        <v>0.047089361375378</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-113240</t>
+          <t>20250720-034022</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
-        <v>237.352374792099</v>
+        <v>1291.233800649643</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1142283833275238</v>
+        <v>0.1143711172044276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.740050196647644</v>
+        <v>0.8035225868225098</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7280765771865845</v>
+        <v>0.7974050641059875</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7267755270004272</v>
+        <v>0.7963472604751587</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7265782356262207</v>
+        <v>0.793731689453125</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0479230806231498</v>
+        <v>0.0528817549347877</v>
       </c>
       <c r="K6" t="n">
-        <v>66.14930510520935</v>
+        <v>66.0873384475708</v>
       </c>
       <c r="L6" t="n">
-        <v>2.643260717391968</v>
+        <v>2.876997470855713</v>
       </c>
       <c r="M6" t="n">
-        <v>12.28411769866943</v>
+        <v>12.46230912208557</v>
       </c>
       <c r="N6" t="n">
-        <v>12.41025185585022</v>
+        <v>13.02114868164062</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009474052750508799</v>
+        <v>0.0103118188919559</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0440290956941556</v>
+        <v>0.044667774631131</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0444811894474918</v>
+        <v>0.0466707838051635</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-113910</t>
+          <t>20250720-040635</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-large_idd20k.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-large_idd20k.xlsx
@@ -594,53 +594,53 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>211.2076306343078</v>
+        <v>209.3222594261169</v>
       </c>
       <c r="D2" t="n">
-        <v>1.740000009536743</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0445255056644479</v>
+        <v>0.044043140951544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8009325861930847</v>
+        <v>0.8009699583053589</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7887858748435974</v>
+        <v>0.7904765009880066</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7883997559547424</v>
+        <v>0.7894155979156494</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7872225642204285</v>
+        <v>0.7882975935935974</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0429387725889682</v>
+        <v>0.0408330038189888</v>
       </c>
       <c r="K2" t="n">
-        <v>99.792870759964</v>
+        <v>93.17139601707458</v>
       </c>
       <c r="L2" t="n">
-        <v>2.791815280914306</v>
+        <v>2.471015930175781</v>
       </c>
       <c r="M2" t="n">
-        <v>24.09911966323853</v>
+        <v>24.28282070159912</v>
       </c>
       <c r="N2" t="n">
-        <v>15.96792364120483</v>
+        <v>16.16968464851379</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0100065063832054</v>
+        <v>0.0088566879217769</v>
       </c>
       <c r="P2" t="n">
-        <v>0.086376772986518</v>
+        <v>0.0870351996473086</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0572327012229563</v>
+        <v>0.0579558589552465</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-060006</t>
+          <t>20250723-165839</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -715,53 +715,53 @@
         <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>315.7411439418793</v>
+        <v>317.2615060806274</v>
       </c>
       <c r="D3" t="n">
-        <v>2.930000066757202</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0438074938751555</v>
+        <v>0.0442046496916461</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8060427904129028</v>
+        <v>0.8060405254364014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7941439151763916</v>
+        <v>0.7937124371528625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7936789989471436</v>
+        <v>0.7934112548828125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.793429970741272</v>
+        <v>0.7930727005004883</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0426222570240497</v>
+        <v>0.0440335646271705</v>
       </c>
       <c r="K3" t="n">
-        <v>91.62892079353333</v>
+        <v>92.25662302970886</v>
       </c>
       <c r="L3" t="n">
-        <v>2.459702014923096</v>
+        <v>2.564070224761963</v>
       </c>
       <c r="M3" t="n">
-        <v>23.98131370544434</v>
+        <v>23.67836022377014</v>
       </c>
       <c r="N3" t="n">
-        <v>15.63449311256409</v>
+        <v>15.61522746086121</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008816136254204601</v>
+        <v>0.0091902158593618</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0859545294101947</v>
+        <v>0.08486867463716891</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0560376097224519</v>
+        <v>0.0559685572073878</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-060635</t>
+          <t>20250723-170501</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -836,53 +836,53 @@
         <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>226.960597038269</v>
+        <v>225.6634287834167</v>
       </c>
       <c r="D4" t="n">
-        <v>2.200000047683716</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="E4" t="n">
-        <v>0.044130506996925</v>
+        <v>0.0440338043352731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8010107278823853</v>
+        <v>0.8010106086730957</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7932020425796509</v>
+        <v>0.7931737899780273</v>
       </c>
       <c r="H4" t="n">
-        <v>0.792592465877533</v>
+        <v>0.7924994230270386</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7919518947601318</v>
+        <v>0.7918925881385803</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0432083085179328</v>
+        <v>0.0452971495687961</v>
       </c>
       <c r="K4" t="n">
-        <v>112.3295249938965</v>
+        <v>92.5021493434906</v>
       </c>
       <c r="L4" t="n">
-        <v>2.516344308853149</v>
+        <v>2.547816038131714</v>
       </c>
       <c r="M4" t="n">
-        <v>23.64404797554016</v>
+        <v>24.26694750785828</v>
       </c>
       <c r="N4" t="n">
-        <v>15.51453685760498</v>
+        <v>16.36807441711426</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0090191552288643</v>
+        <v>0.0091319571259201</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0847456916686027</v>
+        <v>0.08697830647977869</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0556076589878314</v>
+        <v>0.0586669333946747</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-061521</t>
+          <t>20250723-171348</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>360.0477292537689</v>
+        <v>433.4886786937714</v>
       </c>
       <c r="D5" t="n">
-        <v>2.079999923706055</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.044245616399816</v>
+        <v>0.0442795008420943</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8075137138366699</v>
+        <v>0.8076472878456116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7940849661827087</v>
+        <v>0.7942250370979309</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7929789423942566</v>
+        <v>0.7930629849433899</v>
       </c>
       <c r="I5" t="n">
-        <v>0.792610228061676</v>
+        <v>0.7928813695907593</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0429855287075042</v>
+        <v>0.0430994257330894</v>
       </c>
       <c r="K5" t="n">
-        <v>92.37460350990295</v>
+        <v>112.7430307865143</v>
       </c>
       <c r="L5" t="n">
-        <v>2.557039499282837</v>
+        <v>2.526617288589477</v>
       </c>
       <c r="M5" t="n">
-        <v>24.06416416168213</v>
+        <v>23.99846267700196</v>
       </c>
       <c r="N5" t="n">
-        <v>16.06493973731995</v>
+        <v>15.62764286994934</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0091650161264617</v>
+        <v>0.0090559759447651</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0862514844504735</v>
+        <v>0.08601599525807151</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0575804291660213</v>
+        <v>0.0560130568815388</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-062238</t>
+          <t>20250723-172026</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1078,53 +1078,53 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>135.3923170566559</v>
+        <v>136.2500581741333</v>
       </c>
       <c r="D6" t="n">
-        <v>1.820000052452088</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0442889377474784</v>
+        <v>0.0442327154179413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7969760894775391</v>
+        <v>0.7967302799224854</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7910020351409912</v>
+        <v>0.7907745838165283</v>
       </c>
       <c r="H6" t="n">
-        <v>0.79154372215271</v>
+        <v>0.7913457751274109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7904616594314575</v>
+        <v>0.7901772856712341</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0445060729980468</v>
+        <v>0.0415808968245983</v>
       </c>
       <c r="K6" t="n">
-        <v>92.7372362613678</v>
+        <v>92.1394956111908</v>
       </c>
       <c r="L6" t="n">
-        <v>2.490730285644531</v>
+        <v>2.46909761428833</v>
       </c>
       <c r="M6" t="n">
-        <v>24.31395816802979</v>
+        <v>23.87763452529907</v>
       </c>
       <c r="N6" t="n">
-        <v>15.96870017051697</v>
+        <v>16.33191061019897</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0089273486940664</v>
+        <v>0.0088498122375925</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08714680346964079</v>
+        <v>0.08558291944551639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0572354844821396</v>
+        <v>0.05853731401505</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-063129</t>
+          <t>20250723-173111</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>1698.137496471405</v>
+        <v>1347.507011175156</v>
       </c>
       <c r="D2" t="n">
-        <v>2.809999942779541</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1565913549240897</v>
+        <v>0.1558079827162954</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8097259402275085</v>
+        <v>0.8058920502662659</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7953490018844604</v>
+        <v>0.7902858257293701</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7930800914764404</v>
+        <v>0.7875452637672424</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7871069312095642</v>
+        <v>0.7866822481155396</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0737729668617248</v>
+        <v>0.0743833407759666</v>
       </c>
       <c r="K2" t="n">
-        <v>275.2233033180237</v>
+        <v>275.9223430156708</v>
       </c>
       <c r="L2" t="n">
-        <v>3.861471176147461</v>
+        <v>3.816813230514526</v>
       </c>
       <c r="M2" t="n">
-        <v>13.95684814453125</v>
+        <v>13.6521360874176</v>
       </c>
       <c r="N2" t="n">
-        <v>16.93196058273315</v>
+        <v>17.00558614730835</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0138403984808152</v>
+        <v>0.0136803341595502</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0500245453209005</v>
+        <v>0.0489323874100989</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0606880307624844</v>
+        <v>0.0609519216749403</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-115007</t>
+          <t>20250721-175034</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>1326.610040903091</v>
+        <v>1591.893430709839</v>
       </c>
       <c r="D3" t="n">
-        <v>2.839999914169312</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1563637068249144</v>
+        <v>0.1574837475542038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.799574613571167</v>
+        <v>0.8051925897598267</v>
       </c>
       <c r="G3" t="n">
-        <v>0.787930428981781</v>
+        <v>0.7972016334533691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7850078344345093</v>
+        <v>0.7950171828269958</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7801093459129333</v>
+        <v>0.792414665222168</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0790983214974403</v>
+        <v>0.07086779177188871</v>
       </c>
       <c r="K3" t="n">
-        <v>276.4615280628204</v>
+        <v>275.3668963909149</v>
       </c>
       <c r="L3" t="n">
-        <v>4.02959156036377</v>
+        <v>4.036093473434448</v>
       </c>
       <c r="M3" t="n">
-        <v>14.17910671234131</v>
+        <v>14.12543821334839</v>
       </c>
       <c r="N3" t="n">
-        <v>16.46771502494812</v>
+        <v>16.34289765357971</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0144429805030959</v>
+        <v>0.0144662848510195</v>
       </c>
       <c r="P3" t="n">
-        <v>0.050821171011976</v>
+        <v>0.0506288108005318</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0590240681897782</v>
+        <v>0.058576694098852</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-122447</t>
+          <t>20250721-181903</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>1397.175152778625</v>
+        <v>1652.217128753662</v>
       </c>
       <c r="D4" t="n">
-        <v>2.869999885559082</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1559421627649238</v>
+        <v>0.1573213049859711</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8057184219360352</v>
+        <v>0.796816885471344</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7937065362930298</v>
+        <v>0.7875039577484131</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7911221981048584</v>
+        <v>0.7855411767959595</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7848518490791321</v>
+        <v>0.7834763526916504</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0697472393512725</v>
+        <v>0.06841230392456051</v>
       </c>
       <c r="K4" t="n">
-        <v>275.853835105896</v>
+        <v>275.246869802475</v>
       </c>
       <c r="L4" t="n">
-        <v>3.642279386520386</v>
+        <v>3.605145692825317</v>
       </c>
       <c r="M4" t="n">
-        <v>13.42474007606506</v>
+        <v>13.84645581245422</v>
       </c>
       <c r="N4" t="n">
-        <v>16.71097755432129</v>
+        <v>17.16639637947083</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0130547648262379</v>
+        <v>0.0129216691499115</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0481173479428855</v>
+        <v>0.0496288738797642</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0598959768972089</v>
+        <v>0.0615283024353793</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-125255</t>
+          <t>20250721-185136</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1728,53 +1728,53 @@
         <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>1400.610742092133</v>
+        <v>1412.434566736221</v>
       </c>
       <c r="D5" t="n">
         <v>2.869999885559082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1566611837063516</v>
+        <v>0.1577669919601508</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7995622158050537</v>
+        <v>0.8044545650482178</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7919187545776367</v>
+        <v>0.7941239476203918</v>
       </c>
       <c r="H5" t="n">
-        <v>0.789287269115448</v>
+        <v>0.7913265228271484</v>
       </c>
       <c r="I5" t="n">
-        <v>0.785477340221405</v>
+        <v>0.787680983543396</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0767068639397621</v>
+        <v>0.07817550003528589</v>
       </c>
       <c r="K5" t="n">
-        <v>276.0336818695068</v>
+        <v>275.9150815010071</v>
       </c>
       <c r="L5" t="n">
-        <v>4.243395328521729</v>
+        <v>4.060283184051514</v>
       </c>
       <c r="M5" t="n">
-        <v>14.05256819725037</v>
+        <v>13.94289875030518</v>
       </c>
       <c r="N5" t="n">
-        <v>16.58019280433655</v>
+        <v>17.34021592140198</v>
       </c>
       <c r="O5" t="n">
-        <v>0.015209302252766</v>
+        <v>0.0145529863227652</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0503676279471339</v>
+        <v>0.0499745474921332</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0594272143524607</v>
+        <v>0.0621513115462436</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-132233</t>
+          <t>20250721-192509</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>1423.49977850914</v>
+        <v>1413.215521097183</v>
       </c>
       <c r="D6" t="n">
         <v>2.779999971389771</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1559107052652458</v>
+        <v>0.1577313851032938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8041864633560181</v>
+        <v>0.8050204515457153</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7903594970703125</v>
+        <v>0.7925274968147278</v>
       </c>
       <c r="H6" t="n">
-        <v>0.787421703338623</v>
+        <v>0.7899947166442871</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7832230925559998</v>
+        <v>0.7866424322128296</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0714063569903373</v>
+        <v>0.0765988826751709</v>
       </c>
       <c r="K6" t="n">
-        <v>276.5493903160095</v>
+        <v>275.1480753421783</v>
       </c>
       <c r="L6" t="n">
-        <v>3.823434829711914</v>
+        <v>4.242442607879639</v>
       </c>
       <c r="M6" t="n">
-        <v>14.03970909118652</v>
+        <v>13.97275376319885</v>
       </c>
       <c r="N6" t="n">
-        <v>16.68345046043396</v>
+        <v>16.63410544395447</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0137040674900068</v>
+        <v>0.0152058874834395</v>
       </c>
       <c r="P6" t="n">
-        <v>0.050321537961242</v>
+        <v>0.0500815547068059</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0597973134782579</v>
+        <v>0.0596204496199084</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-135155</t>
+          <t>20250721-195443</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
-        <v>1219.77889752388</v>
+        <v>1475.353687047958</v>
       </c>
       <c r="D2" t="n">
-        <v>1.720000028610229</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E2" t="n">
-        <v>0.133023727619857</v>
+        <v>0.1334811846415201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7802820205688477</v>
+        <v>0.7878406643867493</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7685856223106384</v>
+        <v>0.7773923873901367</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7668321132659912</v>
+        <v>0.7756935954093933</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7304259538650513</v>
+        <v>0.7554972171783447</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0664063468575477</v>
+        <v>0.0600209943950176</v>
       </c>
       <c r="K2" t="n">
-        <v>225.6952798366546</v>
+        <v>225.5518500804901</v>
       </c>
       <c r="L2" t="n">
-        <v>3.411694526672364</v>
+        <v>3.505536794662476</v>
       </c>
       <c r="M2" t="n">
-        <v>14.50111842155456</v>
+        <v>14.69249105453491</v>
       </c>
       <c r="N2" t="n">
-        <v>19.85474538803101</v>
+        <v>19.18392252922058</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0122282957945245</v>
+        <v>0.0125646480095429</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0519753348442815</v>
+        <v>0.0526612582599817</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0711639619642688</v>
+        <v>0.0687595789577798</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-174928</t>
+          <t>20250722-002448</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
-        <v>959.104038476944</v>
+        <v>1656.735738515854</v>
       </c>
       <c r="D3" t="n">
-        <v>1.690000057220459</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1343037265945564</v>
+        <v>0.1345676259173975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7691758871078491</v>
+        <v>0.7888545989990234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7556921243667603</v>
+        <v>0.7803001999855042</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7538420557975769</v>
+        <v>0.7785050868988037</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7082706093788147</v>
+        <v>0.7244082689285278</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0625451579689979</v>
+        <v>0.0588320046663284</v>
       </c>
       <c r="K3" t="n">
-        <v>225.720867395401</v>
+        <v>225.3339145183563</v>
       </c>
       <c r="L3" t="n">
-        <v>3.26667046546936</v>
+        <v>3.216009140014648</v>
       </c>
       <c r="M3" t="n">
-        <v>15.02986836433411</v>
+        <v>14.87980914115906</v>
       </c>
       <c r="N3" t="n">
-        <v>20.07252693176269</v>
+        <v>20.12422800064087</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0117084962920048</v>
+        <v>0.0115269144803392</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0538704959295129</v>
+        <v>0.0533326492514661</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07194454097405981</v>
+        <v>0.0721298494646626</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-181501</t>
+          <t>20250722-005436</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>1431.434258460998</v>
+        <v>1523.960861206055</v>
       </c>
       <c r="D4" t="n">
-        <v>1.740000009536743</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.135016602774461</v>
+        <v>0.1341684609651565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7716957330703735</v>
+        <v>0.7849432229995728</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7654707431793213</v>
+        <v>0.7780630588531494</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7638850808143616</v>
+        <v>0.7762599587440491</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6993379592895508</v>
+        <v>0.7621093988418579</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06940522789955129</v>
+        <v>0.0667579919099807</v>
       </c>
       <c r="K4" t="n">
-        <v>226.4841458797455</v>
+        <v>232.0330808162689</v>
       </c>
       <c r="L4" t="n">
-        <v>3.49719500541687</v>
+        <v>3.50993275642395</v>
       </c>
       <c r="M4" t="n">
-        <v>14.98471975326538</v>
+        <v>14.74745607376099</v>
       </c>
       <c r="N4" t="n">
-        <v>19.44162273406982</v>
+        <v>20.35016369819641</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0125347491233579</v>
+        <v>0.0125804041448887</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0537086729507719</v>
+        <v>0.0528582654973512</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06968323560598499</v>
+        <v>0.0729396548322452</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-183614</t>
+          <t>20250722-012726</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>1216.168772935867</v>
+        <v>923.8027489185332</v>
       </c>
       <c r="D5" t="n">
         <v>1.720000028610229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1350201421550341</v>
+        <v>0.1327239060124685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7693449258804321</v>
+        <v>0.7668541669845581</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7588349580764771</v>
+        <v>0.7553228139877319</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7572045922279358</v>
+        <v>0.7534446120262146</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7285274267196655</v>
+        <v>0.707763671875</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0610094256699085</v>
+        <v>0.0643775537610054</v>
       </c>
       <c r="K5" t="n">
-        <v>226.6332972049713</v>
+        <v>225.9690895080566</v>
       </c>
       <c r="L5" t="n">
-        <v>3.225802898406982</v>
+        <v>3.353078603744507</v>
       </c>
       <c r="M5" t="n">
-        <v>14.47894549369812</v>
+        <v>14.80483293533325</v>
       </c>
       <c r="N5" t="n">
-        <v>19.38223528862</v>
+        <v>18.91065073013306</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0115620175570142</v>
+        <v>0.0120182028808046</v>
       </c>
       <c r="P5" t="n">
-        <v>0.051895861984581</v>
+        <v>0.0530639173309435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06947037737856621</v>
+        <v>0.067780110143846</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-190519</t>
+          <t>20250722-015811</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C6" t="n">
-        <v>1389.480852365494</v>
+        <v>1118.183375835419</v>
       </c>
       <c r="D6" t="n">
-        <v>1.730000019073486</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1334047686595182</v>
+        <v>0.1333635962353302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7850383520126343</v>
+        <v>0.765902042388916</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7705782651901245</v>
+        <v>0.7568348050117493</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7686198949813843</v>
+        <v>0.7548423409461975</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7107931971549988</v>
+        <v>0.7143456935882568</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0593171939253807</v>
+        <v>0.0605058707296848</v>
       </c>
       <c r="K6" t="n">
-        <v>224.5037460327148</v>
+        <v>225.350555896759</v>
       </c>
       <c r="L6" t="n">
-        <v>3.471880912780762</v>
+        <v>3.193591594696045</v>
       </c>
       <c r="M6" t="n">
-        <v>14.82607507705688</v>
+        <v>14.62271022796631</v>
       </c>
       <c r="N6" t="n">
-        <v>19.36076378822327</v>
+        <v>19.65087032318115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0124440176085331</v>
+        <v>0.0114465648555413</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0531400540396304</v>
+        <v>0.0524111477704885</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0693934185957823</v>
+        <v>0.070433226964807</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-193049</t>
+          <t>20250722-021848</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>3711.526425838471</v>
+        <v>1104.024732589722</v>
       </c>
       <c r="D2" t="n">
-        <v>8.909999847412109</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3326560536476031</v>
+        <v>0.332579357283456</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8079228401184082</v>
+        <v>0.755954384803772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7935408353805542</v>
+        <v>0.7468031644821167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7903481721878052</v>
+        <v>0.7441437244415283</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6549751758575439</v>
+        <v>0.6135891675949097</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1121824532747268</v>
+        <v>0.1082084402441978</v>
       </c>
       <c r="K2" t="n">
-        <v>1853.778037548065</v>
+        <v>1847.97400021553</v>
       </c>
       <c r="L2" t="n">
-        <v>6.067195892333984</v>
+        <v>5.946203708648682</v>
       </c>
       <c r="M2" t="n">
-        <v>33.91516399383545</v>
+        <v>33.35268545150757</v>
       </c>
       <c r="N2" t="n">
-        <v>36.71845149993896</v>
+        <v>36.75135612487793</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0217462218363225</v>
+        <v>0.0213125580955149</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1215597275764711</v>
+        <v>0.1195436754534321</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1316073530463762</v>
+        <v>0.1317252907701717</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-055440</t>
+          <t>20250722-134945</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>2651.728832244873</v>
+        <v>3155.930606365204</v>
       </c>
       <c r="D3" t="n">
         <v>8.909999847412109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3317309279854481</v>
+        <v>0.3318614474227351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8061126470565796</v>
+        <v>0.8082753419876099</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7911288738250732</v>
+        <v>0.797188937664032</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7882347106933594</v>
+        <v>0.7940124869346619</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2141021639108657</v>
+        <v>0.5442082285881042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1155784204602241</v>
+        <v>0.105472594499588</v>
       </c>
       <c r="K3" t="n">
-        <v>1848.615552425384</v>
+        <v>1903.577384233475</v>
       </c>
       <c r="L3" t="n">
-        <v>6.232304096221924</v>
+        <v>5.895935297012329</v>
       </c>
       <c r="M3" t="n">
-        <v>33.53253412246704</v>
+        <v>33.91618537902832</v>
       </c>
       <c r="N3" t="n">
-        <v>36.26391506195069</v>
+        <v>37.11958861351013</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0223380075133402</v>
+        <v>0.0211323845771051</v>
       </c>
       <c r="P3" t="n">
-        <v>0.12018829434576</v>
+        <v>0.1215633884552986</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1299781901862031</v>
+        <v>0.1330451204785309</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-073001</t>
+          <t>20250722-144131</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>2845.503630161285</v>
+        <v>3502.203608512878</v>
       </c>
       <c r="D4" t="n">
-        <v>8.859999656677246</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3315923410866941</v>
+        <v>0.3322401720544566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8071444630622864</v>
+        <v>0.8107722401618958</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8001638650894165</v>
+        <v>0.8010135889053345</v>
       </c>
       <c r="H4" t="n">
-        <v>0.796950101852417</v>
+        <v>0.7982279658317566</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5369940996170044</v>
+        <v>0.6982628703117371</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1055933088064193</v>
+        <v>0.1094812154769897</v>
       </c>
       <c r="K4" t="n">
-        <v>1844.140513658524</v>
+        <v>1841.155631542206</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8802809715271</v>
+        <v>5.949141025543213</v>
       </c>
       <c r="M4" t="n">
-        <v>33.99720335006714</v>
+        <v>33.96782326698303</v>
       </c>
       <c r="N4" t="n">
-        <v>37.05563569068909</v>
+        <v>36.68761682510376</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0210762758836096</v>
+        <v>0.0213230861130581</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1218537754482693</v>
+        <v>0.1217484704909786</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1328158985329358</v>
+        <v>0.1314968344985798</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-084737</t>
+          <t>20250722-160827</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3270,53 +3270,53 @@
         <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>2863.753146409988</v>
+        <v>2871.614633321762</v>
       </c>
       <c r="D5" t="n">
-        <v>8.869999885559082</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3324168510735035</v>
+        <v>0.3330142237246036</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8019478917121887</v>
+        <v>0.8004374504089355</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7922053933143616</v>
+        <v>0.7901514172554016</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7891817092895508</v>
+        <v>0.7870141267776489</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2849306464195251</v>
+        <v>0.613966166973114</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1118238642811775</v>
+        <v>0.10669756680727</v>
       </c>
       <c r="K5" t="n">
-        <v>1854.941435098648</v>
+        <v>1842.453379869461</v>
       </c>
       <c r="L5" t="n">
-        <v>6.167104482650757</v>
+        <v>5.924674034118652</v>
       </c>
       <c r="M5" t="n">
-        <v>34.16125345230103</v>
+        <v>33.88216876983643</v>
       </c>
       <c r="N5" t="n">
-        <v>36.95046210289001</v>
+        <v>36.84747385978699</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0221043171421174</v>
+        <v>0.0212353908032926</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1224417686462402</v>
+        <v>0.1214414651248617</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.132438932268423</v>
+        <v>0.1320697987805985</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-100822</t>
+          <t>20250722-174006</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
-        <v>2908.240720033646</v>
+        <v>3344.720404624939</v>
       </c>
       <c r="D6" t="n">
-        <v>8.960000038146973</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3314920475608424</v>
+        <v>0.3312768394296819</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8051818609237671</v>
+        <v>0.808678925037384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7987508177757263</v>
+        <v>0.8003470301628113</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7954124212265015</v>
+        <v>0.7972804307937622</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4738762080669403</v>
+        <v>0.5435607433319092</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1038564518094062</v>
+        <v>0.1087795346975326</v>
       </c>
       <c r="K6" t="n">
-        <v>1854.765387535095</v>
+        <v>1836.228323459625</v>
       </c>
       <c r="L6" t="n">
-        <v>5.86062479019165</v>
+        <v>5.923750638961792</v>
       </c>
       <c r="M6" t="n">
-        <v>34.0386655330658</v>
+        <v>33.9719557762146</v>
       </c>
       <c r="N6" t="n">
-        <v>36.66395902633667</v>
+        <v>36.23326110839844</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0210058236207586</v>
+        <v>0.0212320811432322</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1220023854231748</v>
+        <v>0.1217632823520236</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1314120395209199</v>
+        <v>0.1298683193849406</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-112938</t>
+          <t>20250722-190116</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>2113.475056409836</v>
+        <v>1616.559000492096</v>
       </c>
       <c r="D2" t="n">
-        <v>7.53000020980835</v>
+        <v>7.489999771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2004082049384261</v>
+        <v>0.2010695868730545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8335310220718384</v>
+        <v>0.8272421956062317</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8238037824630737</v>
+        <v>0.8172556757926941</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8214598298072815</v>
+        <v>0.8148468136787415</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8185414671897888</v>
+        <v>0.8132022023200989</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0801214575767517</v>
+        <v>0.0805350318551063</v>
       </c>
       <c r="K2" t="n">
-        <v>145.0797662734985</v>
+        <v>147.5137145519257</v>
       </c>
       <c r="L2" t="n">
-        <v>4.449892282485962</v>
+        <v>4.392203092575073</v>
       </c>
       <c r="M2" t="n">
-        <v>25.18686151504517</v>
+        <v>25.69559836387634</v>
       </c>
       <c r="N2" t="n">
-        <v>20.31970405578613</v>
+        <v>20.87989830970764</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0159494347042507</v>
+        <v>0.0157426634142475</v>
       </c>
       <c r="P2" t="n">
-        <v>0.09027548930123711</v>
+        <v>0.0920989188669403</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0728304804866886</v>
+        <v>0.0748383451960847</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-154758</t>
+          <t>20250723-010918</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>2647.49517583847</v>
+        <v>1708.485644817352</v>
       </c>
       <c r="D3" t="n">
-        <v>7.53000020980835</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2004749315330781</v>
+        <v>0.2011148479749571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8347631692886353</v>
+        <v>0.8259307146072388</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8276669979095459</v>
+        <v>0.8164503574371338</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8248223066329956</v>
+        <v>0.8142290115356445</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8235999345779419</v>
+        <v>0.8068695664405823</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0806917995214462</v>
+        <v>0.0820352733135223</v>
       </c>
       <c r="K3" t="n">
-        <v>148.261679649353</v>
+        <v>150.6492116451263</v>
       </c>
       <c r="L3" t="n">
-        <v>4.687019109725952</v>
+        <v>4.751471281051636</v>
       </c>
       <c r="M3" t="n">
-        <v>26.01577162742615</v>
+        <v>25.53910708427429</v>
       </c>
       <c r="N3" t="n">
-        <v>20.36695432662964</v>
+        <v>20.4578423500061</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0167993516477632</v>
+        <v>0.0170303630145219</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0932464932882657</v>
+        <v>0.0915380182232053</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0729998362961635</v>
+        <v>0.0733255998208104</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-162734</t>
+          <t>20250723-014041</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3920,53 +3920,53 @@
         <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>1839.283390522003</v>
+        <v>1839.721850633621</v>
       </c>
       <c r="D4" t="n">
-        <v>7.440000057220459</v>
+        <v>7.610000133514404</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2004850770820651</v>
+        <v>0.2012478850389781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8292791843414307</v>
+        <v>0.8314213752746582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8186444044113159</v>
+        <v>0.8256485462188721</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8170033693313599</v>
+        <v>0.8233355283737183</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8111550211906433</v>
+        <v>0.8201094269752502</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0802479013800621</v>
+        <v>0.0806791484355926</v>
       </c>
       <c r="K4" t="n">
-        <v>166.1335399150848</v>
+        <v>145.7918269634247</v>
       </c>
       <c r="L4" t="n">
-        <v>4.352849721908569</v>
+        <v>4.410298109054565</v>
       </c>
       <c r="M4" t="n">
-        <v>25.60110807418823</v>
+        <v>25.66093564033508</v>
       </c>
       <c r="N4" t="n">
-        <v>20.13644218444824</v>
+        <v>20.22043466567993</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0156016119064823</v>
+        <v>0.0158075201041382</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0917602439935062</v>
+        <v>0.0919746797144626</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07217362790124809</v>
+        <v>0.07247467622107499</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-171548</t>
+          <t>20250723-021318</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
-        <v>2474.50227856636</v>
+        <v>2315.17419719696</v>
       </c>
       <c r="D5" t="n">
-        <v>7.480000019073486</v>
+        <v>7.489999771118164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2006429327385766</v>
+        <v>0.2010146820296844</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8359231948852539</v>
+        <v>0.8336628675460815</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8281614780426025</v>
+        <v>0.825701117515564</v>
       </c>
       <c r="H5" t="n">
-        <v>0.825705349445343</v>
+        <v>0.8234530091285706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8218453526496887</v>
+        <v>0.8183148503303528</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0799513906240463</v>
+        <v>0.0813824236392974</v>
       </c>
       <c r="K5" t="n">
-        <v>171.4881372451782</v>
+        <v>149.9424035549164</v>
       </c>
       <c r="L5" t="n">
-        <v>4.43171238899231</v>
+        <v>4.439064264297485</v>
       </c>
       <c r="M5" t="n">
-        <v>25.92628955841064</v>
+        <v>25.83566069602966</v>
       </c>
       <c r="N5" t="n">
-        <v>19.98648571968078</v>
+        <v>20.47271656990052</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0158842737956713</v>
+        <v>0.0159106246032167</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0929257690265614</v>
+        <v>0.0926009343943715</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07163614953290599</v>
+        <v>0.07337891243691939</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-175051</t>
+          <t>20250723-024802</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>2731.289233922958</v>
+        <v>1996.705176353454</v>
       </c>
       <c r="D6" t="n">
         <v>7.570000171661377</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2003984507392434</v>
+        <v>0.2006410338705586</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8363082408905029</v>
+        <v>0.8315010070800781</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8274447917938232</v>
+        <v>0.82716965675354</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8248506784439087</v>
+        <v>0.8251163959503174</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8234127163887024</v>
+        <v>0.8211352229118347</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0799347385764122</v>
+        <v>0.0897149816155433</v>
       </c>
       <c r="K6" t="n">
-        <v>144.7563796043396</v>
+        <v>150.8867709636688</v>
       </c>
       <c r="L6" t="n">
-        <v>4.3884437084198</v>
+        <v>4.799899816513062</v>
       </c>
       <c r="M6" t="n">
-        <v>25.36142635345459</v>
+        <v>25.94520449638367</v>
       </c>
       <c r="N6" t="n">
-        <v>20.16662812232971</v>
+        <v>20.88302040100098</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0157291889190673</v>
+        <v>0.0172039419946704</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0909011697256436</v>
+        <v>0.0929935645031672</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0722818212269882</v>
+        <v>0.07484953548745869</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-183634</t>
+          <t>20250723-033106</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>950.8857963085176</v>
+        <v>1324.228495597839</v>
       </c>
       <c r="D2" t="n">
-        <v>4.949999809265137</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1259468567112217</v>
+        <v>0.1256568544186078</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8135792016983032</v>
+        <v>0.8202721476554871</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8057218790054321</v>
+        <v>0.8123342394828796</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8028199672698975</v>
+        <v>0.8104027509689331</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7999787330627441</v>
+        <v>0.8077232837677002</v>
       </c>
       <c r="J2" t="n">
-        <v>0.058684516698122</v>
+        <v>0.057132638990879</v>
       </c>
       <c r="K2" t="n">
-        <v>84.06671762466431</v>
+        <v>104.7040586471558</v>
       </c>
       <c r="L2" t="n">
-        <v>3.166439056396484</v>
+        <v>3.178575277328491</v>
       </c>
       <c r="M2" t="n">
-        <v>16.62206530570984</v>
+        <v>15.659743309021</v>
       </c>
       <c r="N2" t="n">
-        <v>13.56556963920593</v>
+        <v>13.49572229385376</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0113492439297365</v>
+        <v>0.0113927429294928</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0595772950025442</v>
+        <v>0.0561281122187132</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0486221134021718</v>
+        <v>0.0483717644940994</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-215229</t>
+          <t>20250723-074332</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>1110.801471233368</v>
+        <v>861.2280964851379</v>
       </c>
       <c r="D3" t="n">
-        <v>4.989999771118164</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1260665129456255</v>
+        <v>0.1285046426261343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8184645175933838</v>
+        <v>0.807314395904541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8105575442314148</v>
+        <v>0.7970899343490601</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8085383176803589</v>
+        <v>0.795495867729187</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8059754371643066</v>
+        <v>0.7921802997589111</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0579109862446785</v>
+        <v>0.0554532967507839</v>
       </c>
       <c r="K3" t="n">
-        <v>84.14042377471924</v>
+        <v>104.0459861755371</v>
       </c>
       <c r="L3" t="n">
-        <v>3.158691167831421</v>
+        <v>3.017802476882935</v>
       </c>
       <c r="M3" t="n">
-        <v>15.78366756439209</v>
+        <v>16.32792973518372</v>
       </c>
       <c r="N3" t="n">
-        <v>13.72171425819397</v>
+        <v>13.69926428794861</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0113214737198258</v>
+        <v>0.0108164963329137</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0565722851770325</v>
+        <v>0.0585230456458197</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0491817715347454</v>
+        <v>0.049101305691572</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-221055</t>
+          <t>20250723-080852</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>1423.121651649475</v>
+        <v>1628.546719789505</v>
       </c>
       <c r="D4" t="n">
-        <v>5.099999904632568</v>
+        <v>5.050000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1274474882993145</v>
+        <v>0.1261042479425668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8219746947288513</v>
+        <v>0.8228522539138794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8133401870727539</v>
+        <v>0.8162491917610168</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8117437362670898</v>
+        <v>0.8144360780715942</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8100804090499878</v>
+        <v>0.8124178051948547</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0566738471388816</v>
+        <v>0.0611081272363662</v>
       </c>
       <c r="K4" t="n">
-        <v>97.19948577880859</v>
+        <v>85.64016246795654</v>
       </c>
       <c r="L4" t="n">
-        <v>3.154383420944214</v>
+        <v>3.228168249130249</v>
       </c>
       <c r="M4" t="n">
-        <v>16.90333485603333</v>
+        <v>16.08348870277405</v>
       </c>
       <c r="N4" t="n">
-        <v>15.68528699874878</v>
+        <v>13.84414434432983</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0113060337668251</v>
+        <v>0.0115704955165958</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0605854295915173</v>
+        <v>0.0576469129131686</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.056219666662182</v>
+        <v>0.0496205890477771</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-223222</t>
+          <t>20250723-082608</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C5" t="n">
-        <v>1584.681986093521</v>
+        <v>1266.520245552063</v>
       </c>
       <c r="D5" t="n">
-        <v>5.059999942779541</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.126323490464068</v>
+        <v>0.1259954687087766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8218780755996704</v>
+        <v>0.8189709186553955</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8156746625900269</v>
+        <v>0.8104747533798218</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8137463331222534</v>
+        <v>0.8083791136741638</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8117508888244629</v>
+        <v>0.8054801225662231</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0550873316824436</v>
+        <v>0.0585097186267375</v>
       </c>
       <c r="K5" t="n">
-        <v>84.4327700138092</v>
+        <v>106.230123758316</v>
       </c>
       <c r="L5" t="n">
-        <v>3.003417253494263</v>
+        <v>3.179787635803223</v>
       </c>
       <c r="M5" t="n">
-        <v>16.40593361854553</v>
+        <v>16.49695944786072</v>
       </c>
       <c r="N5" t="n">
-        <v>13.86163353919983</v>
+        <v>13.62085747718811</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0107649363924525</v>
+        <v>0.0113970883003699</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0588026294571524</v>
+        <v>0.059128886909895</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0496832743340495</v>
+        <v>0.0488202776960147</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-225857</t>
+          <t>20250723-085615</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>1171.467784166336</v>
+        <v>1142.075442790985</v>
       </c>
       <c r="D6" t="n">
-        <v>5.090000152587891</v>
+        <v>5.050000190734863</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1260347697034216</v>
+        <v>0.1255659476986952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8134604096412659</v>
+        <v>0.8145276308059692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8083552122116089</v>
+        <v>0.8116478323936462</v>
       </c>
       <c r="H6" t="n">
-        <v>0.807231605052948</v>
+        <v>0.8090830445289612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8041368126869202</v>
+        <v>0.8059902787208557</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0555816851556301</v>
+        <v>0.0557685606181621</v>
       </c>
       <c r="K6" t="n">
-        <v>105.634753704071</v>
+        <v>104.3446533679962</v>
       </c>
       <c r="L6" t="n">
-        <v>3.094919919967652</v>
+        <v>3.330577850341797</v>
       </c>
       <c r="M6" t="n">
-        <v>16.10882806777954</v>
+        <v>16.02370548248291</v>
       </c>
       <c r="N6" t="n">
-        <v>13.80390334129334</v>
+        <v>13.85346627235413</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0110929029389521</v>
+        <v>0.0119375550191462</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0577377350099625</v>
+        <v>0.0574326361379315</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0494763560619832</v>
+        <v>0.0496540009761796</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-232758</t>
+          <t>20250723-092040</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>1400.555305242538</v>
+        <v>1206.085255384445</v>
       </c>
       <c r="D2" t="n">
-        <v>3.869999885559082</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1146068153412718</v>
+        <v>0.1152228672917072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.806735634803772</v>
+        <v>0.8026672005653381</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7994555234909058</v>
+        <v>0.7935678362846375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7976891994476318</v>
+        <v>0.7924494743347168</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7969673871994019</v>
+        <v>0.7889416217803955</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0506798103451728</v>
+        <v>0.0489141047000885</v>
       </c>
       <c r="K2" t="n">
-        <v>67.01188945770264</v>
+        <v>67.41623640060425</v>
       </c>
       <c r="L2" t="n">
-        <v>2.74858832359314</v>
+        <v>2.708637475967407</v>
       </c>
       <c r="M2" t="n">
-        <v>12.68917989730835</v>
+        <v>12.32794737815857</v>
       </c>
       <c r="N2" t="n">
-        <v>13.51380896568298</v>
+        <v>13.18086647987366</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009851571052305099</v>
+        <v>0.0097083780500623</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0454809315315711</v>
+        <v>0.0441861913195647</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0484365912748494</v>
+        <v>0.0472432490318052</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-021836</t>
+          <t>20250723-125557</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
-        <v>1585.715210676193</v>
+        <v>1439.147676467896</v>
       </c>
       <c r="D3" t="n">
-        <v>3.829999923706055</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1143784927594106</v>
+        <v>0.1144036259979773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8094531297683716</v>
+        <v>0.8081387281417847</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8046225309371948</v>
+        <v>0.8023527860641479</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8029451370239258</v>
+        <v>0.8003513813018799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8021563291549683</v>
+        <v>0.799199104309082</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0503431744873523</v>
+        <v>0.0517952740192413</v>
       </c>
       <c r="K3" t="n">
-        <v>68.87248253822327</v>
+        <v>86.66682910919189</v>
       </c>
       <c r="L3" t="n">
-        <v>2.699894428253174</v>
+        <v>2.791884660720825</v>
       </c>
       <c r="M3" t="n">
-        <v>12.62012505531311</v>
+        <v>12.24446773529053</v>
       </c>
       <c r="N3" t="n">
-        <v>12.84334778785706</v>
+        <v>12.99253845214844</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0096770409614809</v>
+        <v>0.010006755056347</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0452334231373229</v>
+        <v>0.0438869811300735</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0460335046159751</v>
+        <v>0.0465682381797435</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-024432</t>
+          <t>20250723-131838</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>1452.101139545441</v>
+        <v>1312.225959300995</v>
       </c>
       <c r="D4" t="n">
-        <v>3.869999885559082</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1139648912262312</v>
+        <v>0.1144158549501862</v>
       </c>
       <c r="F4" t="n">
-        <v>0.807955265045166</v>
+        <v>0.8065243363380432</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7989195585250854</v>
+        <v>0.7973026037216187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7963964343070984</v>
+        <v>0.7951520681381226</v>
       </c>
       <c r="I4" t="n">
-        <v>0.79375159740448</v>
+        <v>0.7938572764396667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.047112550586462</v>
+        <v>0.0486613027751445</v>
       </c>
       <c r="K4" t="n">
-        <v>68.37729287147522</v>
+        <v>66.09625792503357</v>
       </c>
       <c r="L4" t="n">
-        <v>2.683174610137939</v>
+        <v>2.677334785461426</v>
       </c>
       <c r="M4" t="n">
-        <v>12.86145853996277</v>
+        <v>12.38284063339233</v>
       </c>
       <c r="N4" t="n">
-        <v>13.03606986999512</v>
+        <v>13.56663489341736</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0096171132979854</v>
+        <v>0.009596182026743399</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0460984177059597</v>
+        <v>0.0443829413383237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0467242647670075</v>
+        <v>0.0486259315176249</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-031334</t>
+          <t>20250723-134511</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>1416.443036317825</v>
+        <v>1302.215703010559</v>
       </c>
       <c r="D5" t="n">
-        <v>3.640000104904175</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1142938980808505</v>
+        <v>0.1174894960030265</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8091200590133667</v>
+        <v>0.8090646862983704</v>
       </c>
       <c r="G5" t="n">
-        <v>0.800571084022522</v>
+        <v>0.800609827041626</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7985458970069885</v>
+        <v>0.7989130020141602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7946949005126953</v>
+        <v>0.7978998422622681</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0509300678968429</v>
+        <v>0.0490508377552032</v>
       </c>
       <c r="K5" t="n">
-        <v>88.97238945960999</v>
+        <v>66.52769565582275</v>
       </c>
       <c r="L5" t="n">
-        <v>2.804058313369751</v>
+        <v>2.67418360710144</v>
       </c>
       <c r="M5" t="n">
-        <v>12.44246673583984</v>
+        <v>12.86069774627686</v>
       </c>
       <c r="N5" t="n">
-        <v>13.13793182373047</v>
+        <v>13.11742615699768</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0100503882199632</v>
+        <v>0.009584887480650299</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0445966549671679</v>
+        <v>0.0460956908468704</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.047089361375378</v>
+        <v>0.0470158643619988</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-034022</t>
+          <t>20250723-140937</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>1291.233800649643</v>
+        <v>1950.664100646973</v>
       </c>
       <c r="D6" t="n">
-        <v>3.819999933242798</v>
+        <v>3.75</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1143711172044276</v>
+        <v>0.1139374456812287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8035225868225098</v>
+        <v>0.8135025501251221</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7974050641059875</v>
+        <v>0.803949236869812</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7963472604751587</v>
+        <v>0.8020795583724976</v>
       </c>
       <c r="I6" t="n">
-        <v>0.793731689453125</v>
+        <v>0.8004482984542847</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0528817549347877</v>
+        <v>0.0535062551498413</v>
       </c>
       <c r="K6" t="n">
-        <v>66.0873384475708</v>
+        <v>68.27406024932861</v>
       </c>
       <c r="L6" t="n">
-        <v>2.876997470855713</v>
+        <v>2.903874397277832</v>
       </c>
       <c r="M6" t="n">
-        <v>12.46230912208557</v>
+        <v>12.52680850028992</v>
       </c>
       <c r="N6" t="n">
-        <v>13.02114868164062</v>
+        <v>12.90958881378174</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0103118188919559</v>
+        <v>0.0104081519615692</v>
       </c>
       <c r="P6" t="n">
-        <v>0.044667774631131</v>
+        <v>0.0448989551981717</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0466707838051635</v>
+        <v>0.0462709276479632</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-040635</t>
+          <t>20250723-143334</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
